--- a/app/templates/szablon_terminarz.xlsx
+++ b/app/templates/szablon_terminarz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A6FC39-5AA5-41BA-A707-85EF29F4E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016AF006-C110-4DDC-8D01-D66708FEF89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-3132" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>DZIEŃ / DATA TURNIEJU</t>
   </si>
@@ -54,13 +54,25 @@
   </si>
   <si>
     <t>Kategoria</t>
+  </si>
+  <si>
+    <t>NAZWA TURNIEJU</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>MIEJSCOWOŚĆ</t>
+  </si>
+  <si>
+    <t>DZIEŃ I (DATA) (DZIEŃ TYGODNIA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,19 +83,6 @@
     <font>
       <i/>
       <sz val="8"/>
-      <color rgb="FF7A6A5C"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color rgb="FF2D2520"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF7A6A5C"/>
       <name val="Aptos"/>
       <family val="2"/>
@@ -182,6 +181,35 @@
       <family val="2"/>
       <charset val="238"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF7A6A5C"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF7A6A5C"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7A6A5C"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -261,79 +289,79 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -404,80 +432,54 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>323987</xdr:colOff>
+      <xdr:colOff>436260</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123183</xdr:rowOff>
+      <xdr:rowOff>46535</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>330399</xdr:colOff>
+      <xdr:colOff>391031</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>5953</xdr:rowOff>
+      <xdr:rowOff>23268</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Rectangle: Rounded Corners 8">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B34A424-BC4F-11CD-8F68-D077EFD71D94}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2087D7CD-454C-DB87-9107-8FE5C0D3C949}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5675846" y="123183"/>
-          <a:ext cx="2042381" cy="1016840"/>
+          <a:off x="5787710" y="46535"/>
+          <a:ext cx="1990649" cy="1105191"/>
         </a:xfrm>
-        <a:prstGeom prst="roundRect">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:blipFill dpi="0" rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </a:blipFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pl-PL" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -788,7 +790,9 @@
     <row r="2" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
-      <c r="C2" s="26"/>
+      <c r="C2" s="26" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
       <c r="F2" s="22"/>
@@ -797,7 +801,9 @@
     <row r="3" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
-      <c r="C3" s="19"/>
+      <c r="C3" s="19" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="22"/>
@@ -806,7 +812,9 @@
     <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
-      <c r="C4" s="20"/>
+      <c r="C4" s="20" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="22"/>
@@ -843,7 +851,9 @@
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="25"/>
+      <c r="E8" s="25" t="s">
+        <v>13</v>
+      </c>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
     </row>

--- a/app/templates/szablon_terminarz.xlsx
+++ b/app/templates/szablon_terminarz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016AF006-C110-4DDC-8D01-D66708FEF89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DE1C5-69AB-4AE5-8C48-A43A7F3380E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-3132" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -435,22 +435,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>436260</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>46535</xdr:rowOff>
+      <xdr:rowOff>36286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>391031</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>23268</xdr:rowOff>
+      <xdr:colOff>401569</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>234141</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2087D7CD-454C-DB87-9107-8FE5C0D3C949}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A23E3258-5889-98CC-4637-1BF006105504}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -472,8 +472,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5787710" y="46535"/>
-          <a:ext cx="1990649" cy="1105191"/>
+          <a:off x="5860143" y="36286"/>
+          <a:ext cx="1925569" cy="1086855"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/app/templates/szablon_terminarz.xlsx
+++ b/app/templates/szablon_terminarz.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\BAZA_ALL\zprp-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DE1C5-69AB-4AE5-8C48-A43A7F3380E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BBBBDB-BD20-4C2B-BB3C-35D976F5241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-3132" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="strona 1" sheetId="1" r:id="rId1"/>
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -345,9 +345,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -788,44 +785,44 @@
   <sheetData>
     <row r="1" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-    </row>
-    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="20" t="s">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-    </row>
-    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="17" t="s">
         <v>7</v>
       </c>
@@ -836,26 +833,26 @@
       <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="25" t="s">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
     </row>
     <row r="9" spans="1:7" ht="19.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -1201,10 +1198,9 @@
       <c r="A54" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="F5:G6"/>
-    <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A2:B5"/>
@@ -1212,7 +1208,7 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="E8:G8"/>
-    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C2:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35433070866141736" right="0.35433070866141736" top="0.35433070866141736" bottom="0.43307086614173229" header="0.31496062992125984" footer="0.19685039370078741"/>

--- a/app/templates/szablon_terminarz.xlsx
+++ b/app/templates/szablon_terminarz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radek\Desktop\BAZA_ALL\zprp-backend\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BBBBDB-BD20-4C2B-BB3C-35D976F5241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D1C678-C120-4339-9FCC-DE574918C926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="strona 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'strona 1'!$A$1:$G$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'strona 1'!$A$1:$G$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'strona 1'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
@@ -772,7 +772,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -1174,32 +1174,86 @@
       <c r="F42" s="4"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
+    <row r="43" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="8"/>
+    </row>
+    <row r="45" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="9"/>
+    </row>
+    <row r="46" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="8"/>
+    </row>
+    <row r="47" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="8"/>
+    </row>
+    <row r="49" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-    </row>
-    <row r="51" spans="1:1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-    </row>
-    <row r="53" spans="1:1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-    </row>
-    <row r="54" spans="1:1" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+    </row>
+    <row r="57" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="6"/>
+    </row>
+    <row r="60" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="F5:G6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C5:E5"/>
@@ -1217,7 +1271,7 @@
     <oddFooter>&amp;C&amp;8Rewolucja na plaży    •    &amp;P / &amp;N    •    BAZA Beach</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="43" max="16383" man="1"/>
+    <brk id="49" max="16383" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
